--- a/Stats Sheet/Round Gaps/Certamina.xlsx
+++ b/Stats Sheet/Round Gaps/Certamina.xlsx
@@ -361,13 +361,13 @@
     <x:t>Greeples</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>MarcC5M</x:t>
   </x:si>
   <x:si>
     <x:t>MaxEvasion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>SharkeyJaws</x:t>
